--- a/data/trans_orig/IP31KM03_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM03_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>105406</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>96989</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>111620</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>78,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>100286</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>93439</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>105236</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>87,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>118634</t>
+          <t>104231</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109596</t>
+          <t>97984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125648</t>
+          <t>109668</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>218920</t>
+          <t>209637</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209108</t>
+          <t>199758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227161</t>
+          <t>218973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17490</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11276</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25907</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13965</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9015</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20812</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32146</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41958</t>
+          <t>41736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>201395</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>190041</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>209434</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>82,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>165855</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>157281</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>171735</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>89,11%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>84,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>214844</t>
+          <t>161395</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204565</t>
+          <t>154022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224071</t>
+          <t>167305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>380699</t>
+          <t>362789</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>367802</t>
+          <t>350610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391824</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29846</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21807</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>20259</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14379</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28833</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32676</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42955</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>52935</t>
+          <t>49044</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41810</t>
+          <t>38931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65832</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>125093</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>113909</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>135116</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>75,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>156011</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>144744</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>169601</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>76,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138481</t>
+          <t>121967</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127079</t>
+          <t>112480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148605</t>
+          <t>130376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>294494</t>
+          <t>247060</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>276551</t>
+          <t>231604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311083</t>
+          <t>259920</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41429</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31406</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52613</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>32238</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18648</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43505</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17,12%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>23,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>42558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>76845</t>
+          <t>74500</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60256</t>
+          <t>61640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94788</t>
+          <t>89956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>141828</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>132903</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>149284</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>79,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>131351</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>120717</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>138786</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>79,84%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>84,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>152095</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142080</t>
+          <t>123126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159715</t>
+          <t>140713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>283446</t>
+          <t>273977</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>269868</t>
+          <t>261352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295052</t>
+          <t>283778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24337</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16881</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33262</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>33168</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25733</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43802</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25214</t>
+          <t>31830</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>58382</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46776</t>
+          <t>46366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71960</t>
+          <t>68792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>573722</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>554146</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>590560</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>769</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>553504</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>535855</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>570235</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>519742</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602396</t>
+          <t>504214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>642254</t>
+          <t>534529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1177558</t>
+          <t>1093463</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1151284</t>
+          <t>1070568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1203148</t>
+          <t>1117360</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>113102</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>96264</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>132678</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>99630</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>82899</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117279</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>120679</t>
+          <t>98466</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102479</t>
+          <t>83679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142337</t>
+          <t>113994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>220309</t>
+          <t>211568</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194719</t>
+          <t>187671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246583</t>
+          <t>234463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
